--- a/docs/데이터_계보_등록부.xlsx
+++ b/docs/데이터_계보_등록부.xlsx
@@ -543,7 +543,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -650,7 +650,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
-          <t>미노출(화이트리스트 없음)</t>
+          <t>노출(권한 없음)</t>
         </is>
       </c>
       <c r="N26" s="9" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="M27" s="9" t="inlineStr">
         <is>
-          <t>노출(권한 없음)</t>
+          <t>미노출(화이트리스트 없음)</t>
         </is>
       </c>
       <c r="N27" s="9" t="inlineStr">
@@ -2718,6 +2718,7 @@
       </c>
       <c r="O28" s="9" t="inlineStr"/>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
@@ -2738,7 +2739,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
